--- a/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8-9-0</t>
+          <t>3–7–9</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1-8-0</t>
+          <t>0–2–4</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9-1-2</t>
+          <t>2–9–6</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11/25/2021</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4-2-5</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4-6-6</t>
+          <t>6–0–0</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2-3-2</t>
+          <t>6–2–6</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4-0-9</t>
+          <t>8–3–6</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7-0-5</t>
+          <t>8–8–7</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0-2-8</t>
+          <t>8–4–5</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12/02/2021</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8-6-8</t>
+          <t>9–4–1</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0-3-0</t>
+          <t>1–9–2</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0-5-1</t>
+          <t>0–0–0</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4-2-6</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4-1-9</t>
+          <t>9–3–8</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9-2-6</t>
+          <t>8–7–3</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12/09/2021</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4-8-4</t>
+          <t>6–5–3</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2-7-8</t>
+          <t>5–3–9</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1-8-2</t>
+          <t>6–6–6</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8-7-9</t>
+          <t>0–4–6</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4-5-9</t>
+          <t>5–0–4</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>04/28/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9-9-7</t>
+          <t>4–0–6</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12/16/2021</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0-6-1</t>
+          <t>2–4–2</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9-0-7</t>
+          <t>0–4–5</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5-5-4</t>
+          <t>1–8–5</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5-1-1</t>
+          <t>8–9–5</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3–7–9</t>
+          <t>3–0–2</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0–2–4</t>
+          <t>4–1–5</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2–9–6</t>
+          <t>8–1–3</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7–0–0</t>
+          <t>9–2–4</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6–0–0</t>
+          <t>3–9–5</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6–2–6</t>
+          <t>3–7–9</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8–3–6</t>
+          <t>0–2–4</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8–8–7</t>
+          <t>2–9–6</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8–4–5</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9–4–1</t>
+          <t>6–0–0</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1–9–2</t>
+          <t>6–2–6</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0–0–0</t>
+          <t>8–3–6</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7–0–0</t>
+          <t>8–8–7</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9–3–8</t>
+          <t>8–4–5</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8–7–3</t>
+          <t>9–4–1</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6–5–3</t>
+          <t>1–9–2</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5–3–9</t>
+          <t>0–0–0</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6–6–6</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0–4–6</t>
+          <t>9–3–8</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5–0–4</t>
+          <t>8–7–3</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/28/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4–0–6</t>
+          <t>6–5–3</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2–4–2</t>
+          <t>5–3–9</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0–4–5</t>
+          <t>6–6–6</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1–8–5</t>
+          <t>0–4–6</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8–9–5</t>
+          <t>5–0–4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>04/28/2022</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4–0–6</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3–0–2</t>
+          <t>9–4–1</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/26/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4–1–5</t>
+          <t>6–8–4</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8–1–3</t>
+          <t>0–0–8</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9–2–4</t>
+          <t>5–3–9</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3–9–5</t>
+          <t>2–8–7</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>06/02/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3–7–9</t>
+          <t>6–8–3</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0–2–4</t>
+          <t>0–8–2</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2–9–6</t>
+          <t>8–1–9</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7–0–0</t>
+          <t>3–1–7</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6–0–0</t>
+          <t>3–5–5</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6–2–6</t>
+          <t>3–0–2</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8–3–6</t>
+          <t>4–1–5</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8–8–7</t>
+          <t>8–1–3</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8–4–5</t>
+          <t>9–2–4</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9–4–1</t>
+          <t>3–9–5</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1–9–2</t>
+          <t>3–7–9</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0–0–0</t>
+          <t>0–2–4</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7–0–0</t>
+          <t>2–9–6</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9–3–8</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8–7–3</t>
+          <t>6–0–0</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6–5–3</t>
+          <t>6–2–6</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5–3–9</t>
+          <t>8–3–6</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6–6–6</t>
+          <t>8–8–7</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0–4–6</t>
+          <t>8–4–5</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5–0–4</t>
+          <t>9–4–1</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/28/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4–0–6</t>
+          <t>1–9–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>05/09/2022</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0–0–0</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/08/2022</t>
+          <t>06/10/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9–4–1</t>
+          <t>0–3–0</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/07/2022</t>
+          <t>06/09/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6–8–4</t>
+          <t>4–8–6</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0–0–8</t>
+          <t>9–4–1</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/04/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5–3–9</t>
+          <t>6–8–4</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/03/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2–8–7</t>
+          <t>0–0–8</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/02/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6–8–3</t>
+          <t>5–3–9</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/01/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0–8–2</t>
+          <t>2–8–7</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/31/2022</t>
+          <t>06/02/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8–1–9</t>
+          <t>6–8–3</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/30/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3–1–7</t>
+          <t>0–8–2</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/28/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3–5–5</t>
+          <t>8–1–9</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3–0–2</t>
+          <t>3–1–7</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/26/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4–1–5</t>
+          <t>3–5–5</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8–1–3</t>
+          <t>3–0–2</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9–2–4</t>
+          <t>4–1–5</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3–9–5</t>
+          <t>8–1–3</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3–7–9</t>
+          <t>9–2–4</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0–2–4</t>
+          <t>3–9–5</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2–9–6</t>
+          <t>3–7–9</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7–0–0</t>
+          <t>0–2–4</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6–0–0</t>
+          <t>2–9–6</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6–2–6</t>
+          <t>7–0–0</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8–3–6</t>
+          <t>6–0–0</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8–8–7</t>
+          <t>6–2–6</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8–4–5</t>
+          <t>8–3–6</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9–4–1</t>
+          <t>8–8–7</t>
         </is>
       </c>
     </row>
@@ -821,27 +821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1–9–2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>05/09/2022</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0–0–0</t>
+          <t>8–4–5</t>
         </is>
       </c>
     </row>
